--- a/data/trans_orig/IP25A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19558</t>
+          <t>19917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33707</t>
+          <t>34005</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>22684</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36317</t>
+          <t>37381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,73%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46305</t>
+          <t>45427</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66716</t>
+          <t>65868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56778</t>
+          <t>56480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70927</t>
+          <t>70568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46724</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60923</t>
+          <t>60357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>106809</t>
+          <t>107657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127220</t>
+          <t>128098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,32%</t>
+          <t>73,82%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27370</t>
+          <t>26526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19481</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56507</t>
+          <t>56299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50077</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>62837</t>
+          <t>63232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51398</t>
+          <t>50659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>91819</t>
+          <t>92027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109993</t>
+          <t>110127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t>20699</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34050</t>
+          <t>33466</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36186</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51917</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>61154</t>
+          <t>60371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81852</t>
+          <t>80145</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>53,1%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25984</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38630</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>44,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54718</t>
+          <t>54953</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>69086</t>
+          <t>70793</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>89784</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>80663</t>
+          <t>79656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56714</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77329</t>
+          <t>76020</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120745</t>
+          <t>119779</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149538</t>
+          <t>149484</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,4%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>102079</t>
+          <t>103086</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123709</t>
+          <t>124225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>101008</t>
+          <t>102317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121623</t>
+          <t>123399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211541</t>
+          <t>211595</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240334</t>
+          <t>241300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,83%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49068</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>34950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52035</t>
+          <t>51985</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73788</t>
+          <t>73661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97141</t>
+          <t>97285</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,7%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>47946</t>
+          <t>47898</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63732</t>
+          <t>63740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59256</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76010</t>
+          <t>76341</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111164</t>
+          <t>111020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134517</t>
+          <t>134644</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,64%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>19921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>33254</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17759</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30376</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41322</t>
+          <t>41759</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58818</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49018</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35137</t>
+          <t>35157</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47754</t>
+          <t>48137</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75616</t>
+          <t>75471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>93112</t>
+          <t>92675</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,25%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>191056</t>
+          <t>192855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>228986</t>
+          <t>230348</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>212143</t>
+          <t>213551</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>251037</t>
+          <t>250660</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>417527</t>
+          <t>414787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470372</t>
+          <t>467484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>347657</t>
+          <t>346295</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>385587</t>
+          <t>383788</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>348927</t>
+          <t>349304</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387821</t>
+          <t>386413</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>706235</t>
+          <t>709123</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>759080</t>
+          <t>761820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>64,75%</t>
         </is>
       </c>
     </row>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18310</t>
+          <t>17845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31751</t>
+          <t>31860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32192</t>
+          <t>31571</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40798</t>
+          <t>40446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>59821</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48539</t>
+          <t>48430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>62445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47942</t>
+          <t>48563</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61799</t>
+          <t>61302</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101119</t>
+          <t>100602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119625</t>
+          <t>119977</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>62,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13326</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26069</t>
+          <t>25427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>19304</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33801</t>
+          <t>32995</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>36902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54887</t>
+          <t>55295</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,48%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>57265</t>
+          <t>57907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>70057</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,12 +3838,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53104</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67568</t>
+          <t>67601</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>115352</t>
+          <t>114944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134695</t>
+          <t>133337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20939</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34593</t>
+          <t>34643</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>16797</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>30827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41669</t>
+          <t>42082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>61215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,42%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43447</t>
+          <t>43397</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57386</t>
+          <t>57101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46583</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>60442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94908</t>
+          <t>94064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113610</t>
+          <t>113197</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>72,9%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>49399</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71650</t>
+          <t>71335</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>60643</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82892</t>
+          <t>84047</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116918</t>
+          <t>118513</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148299</t>
+          <t>148529</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,3%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106427</t>
+          <t>106742</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>127668</t>
+          <t>128678</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126868</t>
+          <t>125713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150983</t>
+          <t>149117</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,48%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239538</t>
+          <t>239308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270919</t>
+          <t>269324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,44%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55682</t>
+          <t>55095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>73984</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50953</t>
+          <t>51419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>70076</t>
+          <t>70229</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111453</t>
+          <t>111062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139221</t>
+          <t>138953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>55917</t>
+          <t>56842</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75144</t>
+          <t>75731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>56838</t>
+          <t>56685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75961</t>
+          <t>75495</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118519</t>
+          <t>118787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146287</t>
+          <t>146678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10603</t>
+          <t>10552</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>42,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21782</t>
+          <t>21766</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35993</t>
+          <t>35185</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>35342</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>52486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>45,61%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27112</t>
+          <t>27840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37986</t>
+          <t>38037</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>31306</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44709</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61973</t>
+          <t>62595</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79726</t>
+          <t>79739</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,85%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>192023</t>
+          <t>193809</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231685</t>
+          <t>230492</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217074</t>
+          <t>216825</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>258052</t>
+          <t>257732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>419992</t>
+          <t>420491</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>477832</t>
+          <t>476872</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,25%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>367471</t>
+          <t>368664</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>407133</t>
+          <t>405347</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>389391</t>
+          <t>389711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>430369</t>
+          <t>430618</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>768767</t>
+          <t>769727</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>826607</t>
+          <t>826108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,27%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15006</t>
+          <t>15344</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27312</t>
+          <t>28389</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>31653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47574</t>
+          <t>47963</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52189</t>
+          <t>51548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71446</t>
+          <t>71923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,14%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,67%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43666</t>
+          <t>42589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>55972</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>54839</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86024</t>
+          <t>85547</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105281</t>
+          <t>105922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>67,26%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34413</t>
+          <t>33458</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49981</t>
+          <t>50177</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26981</t>
+          <t>26554</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41989</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>64977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86748</t>
+          <t>87656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42478</t>
+          <t>42282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58046</t>
+          <t>59001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60987</t>
+          <t>61284</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75995</t>
+          <t>76422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108687</t>
+          <t>107779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130201</t>
+          <t>130458</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,75%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>24018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36947</t>
+          <t>36784</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47469</t>
+          <t>47065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65172</t>
+          <t>65128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>52,36%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25204</t>
+          <t>25159</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>36899</t>
+          <t>37337</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30421</t>
+          <t>30584</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>43713</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59218</t>
+          <t>59262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76921</t>
+          <t>77325</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>77970</t>
+          <t>77957</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101176</t>
+          <t>100922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77716</t>
+          <t>78550</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101096</t>
+          <t>102616</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162985</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195687</t>
+          <t>193510</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>49,79%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96510</t>
+          <t>96764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119716</t>
+          <t>119729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89883</t>
+          <t>88363</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>112429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>192978</t>
+          <t>195155</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225680</t>
+          <t>227781</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50155</t>
+          <t>50451</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68506</t>
+          <t>68334</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52473</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72161</t>
+          <t>72837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108580</t>
+          <t>109395</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134158</t>
+          <t>134558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53819</t>
+          <t>53991</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72170</t>
+          <t>71874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>56510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76874</t>
+          <t>76344</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117514</t>
+          <t>117114</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143092</t>
+          <t>142277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,53%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18922</t>
+          <t>18292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30566</t>
+          <t>30774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>26462</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40240</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48846</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>65922</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23287</t>
+          <t>23079</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>24933</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38525</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>51453</t>
+          <t>52919</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69995</t>
+          <t>69784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,72%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>240590</t>
+          <t>242468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>282075</t>
+          <t>283645</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>268123</t>
+          <t>268158</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310550</t>
+          <t>309009</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>521540</t>
+          <t>521762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>580802</t>
+          <t>576991</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>46,66%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>312247</t>
+          <t>310677</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>353732</t>
+          <t>351854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>331600</t>
+          <t>333141</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374027</t>
+          <t>373992</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>655670</t>
+          <t>659481</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>714932</t>
+          <t>714710</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>57,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25A_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R-Clase-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2007 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28954</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>22698</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36379</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>27,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>26700</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19917</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34005</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>19775</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>34312</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>29,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>37,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>28954</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>22684</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>37381</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45427</t>
+          <t>46609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>65868</t>
+          <t>65619</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,82%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>54087</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46662</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60343</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>65,13%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>72,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>63785</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>56480</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70568</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56173</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70710</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>70,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>62,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,99%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>54087</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>45660</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60357</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>65,13%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107657</t>
+          <t>107906</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>128098</t>
+          <t>126916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83041</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83041</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83041</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90485</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90485</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90485</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83041</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83041</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83041</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19739</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>33413</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>47,14%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>20356</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>14215</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26526</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>14312</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26848</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,28%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,35%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26155</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>20220</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32652</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,9%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38199</t>
+          <t>37746</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56299</t>
+          <t>55993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>44724</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37466</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>51140</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,1%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>52,86%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57091</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>50921</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63232</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>50599</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>63135</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,72%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,75%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>81,65%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>44724</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>38227</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50659</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>63,1%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>92027</t>
+          <t>92333</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110127</t>
+          <t>110580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>74,55%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>70879</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>70879</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77447</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77447</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77447</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>70879</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>70879</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>70879</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43344</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35800</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>51085</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,68%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27182</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20699</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>33466</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21135</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33806</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,28%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,48%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>43344</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>35951</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>51412</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>60371</t>
+          <t>60807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80145</t>
+          <t>81159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,77%</t>
         </is>
       </c>
     </row>
@@ -1521,72 +1521,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>47560</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>39819</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55104</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,32%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>43,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>32852</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26568</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39335</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26228</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>38899</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>54,72%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,52%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>47560</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>39492</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>54953</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70793</t>
+          <t>69779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>90567</t>
+          <t>90131</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>90904</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>90904</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>90904</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>60034</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>60034</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>60034</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>90904</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>90904</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>90904</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>66005</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>55786</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>75897</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>37,01%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,28%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>68951</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>58517</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>79656</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>59347</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>79558</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>37,73%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>32,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>43,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>66005</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>54938</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>76020</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119779</t>
+          <t>121088</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>149484</t>
+          <t>151569</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>112332</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>102440</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>122551</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62,99%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>57,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>113791</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>103086</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>124225</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103184</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123395</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>62,27%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>112332</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>102317</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>123399</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>62,99%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>211595</t>
+          <t>209510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>241300</t>
+          <t>239991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>178337</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>178337</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>178337</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>276</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>182742</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>182742</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>182742</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>267</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>178337</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>178337</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>178337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>43766</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>35993</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>51968</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>32,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>40805</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>33274</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49116</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>32933</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48224</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>42,06%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,3%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>50,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>43766</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>34950</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>51985</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73661</t>
+          <t>74192</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>97285</t>
+          <t>96192</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67525</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>59323</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>53,3%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>67,66%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>56209</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>47898</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>63740</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>48790</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>64081</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>57,94%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>65,7%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67525</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>59306</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>76341</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>60,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>111020</t>
+          <t>112113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134644</t>
+          <t>134113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>111291</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>111291</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>111291</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>97014</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>97014</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>97014</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>111291</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>111291</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>111291</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>23682</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>17731</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>30249</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>27,07%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>46,17%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>25838</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>19921</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>33254</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>19987</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>32815</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>37,49%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>28,9%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>23682</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>17376</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>30356</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>36,15%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41759</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>58992</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,88%</t>
         </is>
       </c>
     </row>
@@ -2555,67 +2555,67 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>41831</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>35264</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>47782</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>63,85%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>53,83%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>72,93%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
           <t>43083</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>35667</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>49000</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>36106</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>48934</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>62,51%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>51,75%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>71,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>41831</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>35157</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>48137</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>63,85%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75471</t>
+          <t>75442</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>92675</t>
+          <t>94077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>65513</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>68921</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>68921</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>68921</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>65513</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>213629</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>251045</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>35,61%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>41,84%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>209832</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>192855</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>230348</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>191170</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>229141</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>33,44%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>231906</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>213551</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>250660</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>38,65%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>414787</t>
+          <t>416752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>467484</t>
+          <t>469614</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>556</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>368058</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>348919</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>386335</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>61,35%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>58,16%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>64,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>550</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>366811</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>346295</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>383788</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>347502</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>385473</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>63,61%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>60,05%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>66,56%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>556</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>368058</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>349304</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>386413</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>61,35%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>66,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>709123</t>
+          <t>706993</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>761820</t>
+          <t>759855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>599964</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>599964</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>599964</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>858</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>576643</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>576643</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>576643</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>902</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>599964</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>599964</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>599964</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3172,13 +3172,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2012 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25058</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>18991</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32221</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>40,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>24654</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17845</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31860</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>18429</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>31459</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,71%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>25058</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>18832</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>31571</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>41081</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59821</t>
+          <t>59917</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,35%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>55076</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47913</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>61143</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>68,73%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>59,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55636</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48430</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62445</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48831</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>61861</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,29%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,32%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>77,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>55076</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48563</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>61302</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100602</t>
+          <t>100506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119977</t>
+          <t>119342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80134</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80134</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80134</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>80290</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>80290</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>80290</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80134</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80134</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80134</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25826</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19429</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32618</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>22,36%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>37,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19304</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13277</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25427</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13201</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26749</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>23,16%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,93%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>30,51%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25826</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19304</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32995</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>36225</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55295</t>
+          <t>55174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>61079</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>54287</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67476</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,28%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>62,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>77,64%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>64030</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57907</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>70057</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>56585</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>70133</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>76,84%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,49%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,07%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>61079</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>53910</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>67601</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,28%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114944</t>
+          <t>115065</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133337</t>
+          <t>134014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>78,72%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>86905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>86905</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>86905</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>83334</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>83334</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>83334</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>86905</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>86905</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>86905</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>17600</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31010</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>22,79%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,15%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>27238</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>20939</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34643</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>21018</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>34428</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>34,9%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>44,39%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>23933</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>16797</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30827</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>30,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42082</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61215</t>
+          <t>61657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53306</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46229</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>59639</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>77,21%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>50802</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>43397</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>57101</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>43612</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>57022</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>65,1%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>55,61%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>73,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>53306</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>46412</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>60442</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>69,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>94064</t>
+          <t>93622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113197</t>
+          <t>113412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,9%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77239</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>78040</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>78040</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>78040</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77239</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>71901</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>60312</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>83905</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>60604</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>49399</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>71335</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>50302</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71010</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,74%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>71901</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>60643</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>84047</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>118513</t>
+          <t>117722</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148529</t>
+          <t>149627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>137859</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>125855</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>149448</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>65,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>60,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>71,25%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>117473</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106742</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128678</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>107067</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>127775</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,26%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>137859</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>125713</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>149117</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>60,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,09%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239308</t>
+          <t>238210</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269324</t>
+          <t>270115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,65%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>209760</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>209760</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>209760</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>178077</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>178077</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>178077</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>209760</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>209760</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>209760</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60850</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>51293</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>70528</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>40,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>64475</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>55095</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73984</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>55182</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>74215</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>49,28%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>42,11%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>56,55%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>60850</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>51419</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>70229</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,95%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111062</t>
+          <t>112871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138953</t>
+          <t>139249</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,03%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66064</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>56386</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75621</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,05%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>59,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>66351</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56842</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>75731</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>56611</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>75644</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>50,72%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,45%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>57,89%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>66064</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>56685</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75495</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>52,05%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118787</t>
+          <t>118491</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146678</t>
+          <t>144869</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,21%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>126914</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>126914</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>126914</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>130826</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>130826</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>130826</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>126914</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>126914</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>126914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28546</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>22165</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>35048</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>42,93%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>33,34%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>15435</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>10552</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>20749</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>10511</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>21120</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>31,77%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42,7%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>21766</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>35185</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52486</t>
+          <t>52703</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,61%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37945</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31443</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44326</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>57,07%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>66,66%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>33154</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>27840</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38037</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>27469</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>38078</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>68,23%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>57,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,28%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>37945</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>31306</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>44725</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>57,07%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>62595</t>
+          <t>62378</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79739</t>
+          <t>78922</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>68,58%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>66491</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>48589</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>48589</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>48589</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>66491</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>66491</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>66491</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>236114</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>215679</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>255255</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>33,31%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>301</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>211711</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>193809</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>230492</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>192379</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>232808</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>32,35%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>38,47%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>236114</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>216825</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>257732</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>420491</t>
+          <t>418852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>476872</t>
+          <t>476484</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -5528,72 +5528,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>411329</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>392188</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>431764</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>63,53%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>60,57%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>66,69%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>562</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>387445</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>368664</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>405347</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>366348</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>406777</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>64,67%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>61,53%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>67,65%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>411329</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>389711</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>430618</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>769727</t>
+          <t>770115</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>826108</t>
+          <t>827747</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,4%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>647443</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>647443</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>647443</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>863</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>599156</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>599156</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>599156</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>647443</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>647443</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>647443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5807,13 +5807,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si emplean 2 horas o más en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2016 (tasa de respuesta: 98,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39812</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31765</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>47198</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21377</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15344</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>28389</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15564</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>29213</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>30,12%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>39812</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31653</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>47963</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51548</t>
+          <t>51008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71923</t>
+          <t>71532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,43%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>46680</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39294</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54727</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,97%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>45,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>76</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>49601</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>42589</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>55634</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>41765</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>55414</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>69,88%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,38%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46680</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38529</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>54839</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>53,97%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85547</t>
+          <t>85938</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>105922</t>
+          <t>106462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -6218,57 +6218,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86492</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86492</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86492</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70978</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70978</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70978</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86492</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86492</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33964</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26975</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>42371</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>32,98%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,2%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>41,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>33458</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>50177</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>34595</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>49900</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>45,52%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,27%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33964</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>26554</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>41692</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>32,98%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>53,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>64884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>87152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,59%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>69012</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60605</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76001</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>67,02%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>58,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73,8%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>50369</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>42282</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>59001</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>42559</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>57864</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>54,48%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>45,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>63,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>69012</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>61284</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76422</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>67,02%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107779</t>
+          <t>108283</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>130551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>102976</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>102976</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>102976</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>92459</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>92459</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>92459</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>102976</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>102976</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>102976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30237</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23324</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36994</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,62%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>25755</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19685</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31863</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>20091</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>32012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>55,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>30237</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24018</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36784</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47065</t>
+          <t>46881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65128</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,33%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37131</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30374</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>44044</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>55,12%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,38%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>31267</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>25159</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37337</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>25010</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>36931</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>54,83%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>44,12%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>37131</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30584</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>43350</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>55,12%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77325</t>
+          <t>77509</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,31%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>67368</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>67368</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>67368</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>57022</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>57022</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>57022</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>67368</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>67368</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>67368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>89635</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>78183</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>100673</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>40,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>52,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>89056</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>77957</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>100922</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>77880</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>101044</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>45,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>39,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>51,05%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>89635</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>78550</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>102616</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160884</t>
+          <t>164316</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193510</t>
+          <t>195054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>101344</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>90306</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>112796</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59,06%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108630</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>96764</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>119729</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>96642</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>119806</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>54,95%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>48,95%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>101344</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>88363</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>112429</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>53,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195155</t>
+          <t>193611</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227781</t>
+          <t>224349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>57,72%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>190979</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>190979</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>190979</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>197686</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>197686</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>197686</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>272</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>190979</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>190979</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>190979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>61872</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>53234</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>71907</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>41,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>55,59%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>59388</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>50451</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>68334</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>50398</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>68023</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>48,55%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>61872</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>53003</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>72837</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109395</t>
+          <t>107692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134558</t>
+          <t>134321</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,37%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>67475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>57440</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>76113</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>52,17%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>44,41%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>62937</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>53991</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>71874</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>54302</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>71927</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>51,45%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>44,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58,76%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>67475</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>56510</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>76344</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>52,17%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>117114</t>
+          <t>117351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>142277</t>
+          <t>143980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>57,21%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>129347</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>122325</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>122325</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>122325</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>129347</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>129347</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>129347</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>33295</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>26815</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>40112</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>41,26%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>61,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>24217</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>18292</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>30774</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>18578</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>30928</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>44,97%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>33,97%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>57,14%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>33295</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>26462</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>40054</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>48406</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65922</t>
+          <t>66431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -7820,72 +7820,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31692</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24875</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>38172</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>48,77%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>38,28%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>58,74%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>29636</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>23079</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>35561</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>22925</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>35275</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>55,03%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>42,86%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>66,03%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>31692</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>24933</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>38525</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>48,77%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>65,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52919</t>
+          <t>52410</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69784</t>
+          <t>70435</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>59,27%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>64987</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>64987</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>64987</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>53853</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>53853</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>53853</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>64987</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>64987</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>64987</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>288817</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>269358</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>311293</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>41,95%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>48,48%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>388</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>261882</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>242468</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>283645</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>242364</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>282660</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>44,06%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>47,73%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>288817</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>268158</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>309009</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>521762</t>
+          <t>522606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>576991</t>
+          <t>578628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,8%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>353333</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>330857</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>372792</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>55,02%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>51,52%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>58,05%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>332440</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>310677</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>351854</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>311662</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>351958</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>55,94%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>52,27%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>353333</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>333141</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>373992</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>55,02%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>659481</t>
+          <t>657844</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>714710</t>
+          <t>713866</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>642150</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>642150</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>642150</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>891</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>594322</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>594322</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>594322</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>918</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>642150</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>642150</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>642150</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
